--- a/entregables/gestion-proyectos/Historia_de_usuario_Rehavid_v15.xlsx
+++ b/entregables/gestion-proyectos/Historia_de_usuario_Rehavid_v15.xlsx
@@ -35,7 +35,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Supervisor Contactabilidad'!$9:$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Gestor de Datos 1'!$A$9:$I$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'Gestor de Datos 1'!$9:$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Gestor de Datos 2'!$A$9:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Gestor de Datos 2'!$A$9:$I$18</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="8">'Gestor de Datos 2'!$9:$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Diseñador'!$A$9:$I$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'Diseñador'!$9:$9</definedName>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Abra la aplicación en una ventana privada (arranca en la guía) y recorra «Los módulos, uno a uno»: texto, pantallazo y botón «Abrir» de cada módulo, y el resumen «El total del app».</t>
+          <t>Abra la aplicación en una ventana privada (arranca en la guía) y recorra «Los módulos, uno a uno: qué hace cada botón»: texto, lista de botones y funciones, pantallazo y botón «Abrir» de cada módulo, y «El total del app».</t>
         </is>
       </c>
       <c r="E10" s="10" t="inlineStr">
@@ -4630,12 +4630,12 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Resolver un ajuste como dirección</t>
+          <t>Resolver un ajuste desde «Para resolver como dirección»</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>En Mi trabajo cambie el selector «Rol» a un cargo con ajustes propuestos, o provoque uno; use «Resolver ajuste» y pruebe las cuatro decisiones.</t>
+          <t>Abra Mi trabajo con su sesión: la sección «Para resolver como dirección» lista los ajustes de todos los cargos (en la base demostrativa, el Tablero BI de DEM-001). Use «Resolver ajuste» y pruebe las cuatro decisiones.</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Negociar capacidad con un líder</t>
+          <t>Negociar capacidad desde «Para resolver como dirección»</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Provoque un ajuste y resuélvalo con contrapropuesta; observe el estado que queda.</t>
+          <t>Su Mi trabajo trae la sección «Para resolver como dirección» con los ajustes de todos los cargos. Resuelva el del Tablero BI demostrativo con contrapropuesta; observe el estado que queda.</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -7322,7 +7322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -7495,17 +7495,17 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Verificar el estado vacío de Mi trabajo</t>
+          <t>Revisar su bandeja demostrativa</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Abra Mi trabajo en su sesión, sin productos a cargo.</t>
+          <t>Abra Mi trabajo en su sesión.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>Estado vacío claro, sin asignaciones de otros cargos.</t>
+          <t>La base demostrativa trae el «Tablero de control de indicadores» (DEM-002) reasignado a su cargo por la dirección, en «Pendiente de aceptación», para que practique el flujo completo.</t>
         </is>
       </c>
       <c r="F11" s="19" t="n"/>
@@ -7524,17 +7524,17 @@
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Recibir un producto por reasignación</t>
+          <t>Aceptar la asignación reasignada</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Pida a la dirección reasignar el tablero a su cargo («Reasignar cargo» en la tarjeta) y revise Mi trabajo.</t>
+          <t>En esa tarjeta use «Aceptar asignación» declarando tiempo y capacidad.</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>La asignación vuelve a «Pendiente de aceptación» a nombre de su cargo y los botones de aceptar aparecen en su bandeja. PENDIENTE reconocido de su N°3/4: solicitar la reasignación desde su propio cargo aún no existe — verifique si al menos la aceptación tras la reasignación ya funciona y priorice lo que falte.</t>
+          <t>La asignación pasa a Aceptada a nombre de su cargo y aparecen los botones de ejecución («Actualizar», «Hitos», «Requisitos de información»).</t>
         </is>
       </c>
       <c r="F12" s="19" t="n"/>
@@ -7548,22 +7548,22 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Épica 7 · Ejecución: avances y retrasos («Actualizar»)</t>
+          <t>Épica 4 · Aceptación y negociación de capacidad</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Actualizar el producto recibido</t>
+          <t>Recibir un producto por reasignación</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Con la asignación aceptada, use «Actualizar» para un avance con horas.</t>
+          <t>Pida a la dirección reasignar el tablero a su cargo («Reasignar cargo» en la tarjeta) y revise Mi trabajo.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Solo su cargo (o la dirección) puede actualizarlo; queda a nombre del cargo.</t>
+          <t>La asignación vuelve a «Pendiente de aceptación» a nombre de su cargo y los botones de aceptar aparecen en su bandeja. PENDIENTE reconocido de su N°3/4: solicitar la reasignación desde su propio cargo aún no existe — verifique si al menos la aceptación tras la reasignación ya funciona y priorice lo que falte.</t>
         </is>
       </c>
       <c r="F13" s="19" t="n"/>
@@ -7582,17 +7582,17 @@
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Comprobar el bloqueo sobre productos ajenos</t>
+          <t>Actualizar el producto recibido</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Intente actualizar un producto de otro cargo desde Actividades.</t>
+          <t>Con la asignación aceptada, use «Actualizar» para un avance con horas.</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
         <is>
-          <t>Los botones aparecen deshabilitados con la razón.</t>
+          <t>Solo su cargo (o la dirección) puede actualizarlo; queda a nombre del cargo.</t>
         </is>
       </c>
       <c r="F14" s="19" t="n"/>
@@ -7606,22 +7606,22 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Transversal · Resumen, Actividades y Calendario</t>
+          <t>Épica 7 · Ejecución: avances y retrasos («Actualizar»)</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Consultar Resumen y Actividades</t>
+          <t>Comprobar el bloqueo sobre productos ajenos</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Recorra el Resumen (clic en gráficos) y Actividades en tablero y lista.</t>
+          <t>Intente actualizar un producto de otro cargo desde Actividades.</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>La consulta es libre; los filtros y las píldoras «Mis actividades» acotan a su cargo.</t>
+          <t>Los botones aparecen deshabilitados con la razón.</t>
         </is>
       </c>
       <c r="F15" s="19" t="n"/>
@@ -7640,17 +7640,17 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>Descargar un conjunto</t>
+          <t>Consultar Resumen y Actividades</t>
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>Descargue Productos desde Bases y auditoría.</t>
+          <t>Recorra el Resumen (clic en gráficos) y Actividades en tablero y lista.</t>
         </is>
       </c>
       <c r="E16" s="10" t="inlineStr">
         <is>
-          <t>La descarga funciona para cualquier cargo; la edición sigue restringida.</t>
+          <t>La consulta es libre; los filtros y las píldoras «Mis actividades» acotan a su cargo.</t>
         </is>
       </c>
       <c r="F16" s="19" t="n"/>
@@ -7664,22 +7664,22 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Veredicto · ¿Lista para producción?</t>
+          <t>Transversal · Resumen, Actividades y Calendario</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Dar el veredicto de salida a producción</t>
+          <t>Descargar un conjunto</t>
         </is>
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>Termine las actividades de esta pestaña, registre sus observaciones y vaya a la pestaña «Resumen de observaciones»: diligencie su fila en la tabla «Decisión de salida a producción» (Sí · Con ajustes menores · No) con sus condiciones.</t>
+          <t>Descargue Productos desde Bases y auditoría.</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>Cada cargo deja un veredicto explícito. La versión sale a producción solo si ningún cargo responde «No» y las condiciones registradas quedan acordadas con la dirección.</t>
+          <t>La descarga funciona para cualquier cargo; la edición sigue restringida.</t>
         </is>
       </c>
       <c r="F17" s="19" t="n"/>
@@ -7687,18 +7687,46 @@
       <c r="H17" s="20" t="n"/>
       <c r="I17" s="20" t="n"/>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="18" t="n">
+        <v>9</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Veredicto · ¿Lista para producción?</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>Dar el veredicto de salida a producción</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Termine las actividades de esta pestaña, registre sus observaciones y vaya a la pestaña «Resumen de observaciones»: diligencie su fila en la tabla «Decisión de salida a producción» (Sí · Con ajustes menores · No) con sus condiciones.</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Cada cargo deja un veredicto explícito. La versión sale a producción solo si ningún cargo responde «No» y las condiciones registradas quedan acordadas con la dirección.</t>
+        </is>
+      </c>
+      <c r="F18" s="19" t="n"/>
+      <c r="G18" s="19" t="n"/>
+      <c r="H18" s="20" t="n"/>
+      <c r="I18" s="20" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Fuente: Especificación funcional y flujograma del proceso de gestión de proyectos, versión 1.1, Rehavid S.A.S. Tercera ronda sobre la versión 15 (simplificada a cuatro pestañas, con botón único «Actualizar»). Cada cargo cierra sus hallazgos de la segunda ronda (CORREGIDO o PENDIENTE), revisa su base de alimentación y da su veredicto de salida a producción. Los pasos 1 a 11 corresponden al numeral 7 de la especificación. Traslade cada observación a la pestaña «Resumen de observaciones» con el N° de la fila.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A9:I17"/>
+  <autoFilter ref="A9:I18"/>
   <mergeCells count="10">
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A19:I19"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="A5:I5"/>
@@ -7707,12 +7735,13 @@
     <mergeCell ref="A6:I6"/>
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A20:I20"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F10:F17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Seleccione: Sí, No, Parcial o No aplica." promptTitle="¿Funciona?" prompt="Seleccione: Sí, No, Parcial o No aplica." type="list">
+    <dataValidation sqref="F10:F18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Seleccione: Sí, No, Parcial o No aplica." promptTitle="¿Funciona?" prompt="Seleccione: Sí, No, Parcial o No aplica." type="list">
       <formula1>"Sí,No,Parcial,No aplica"</formula1>
     </dataValidation>
-    <dataValidation sqref="G10:G17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Califique con un entero de 1 a 5." promptTitle="Claridad (1-5)" prompt="1 = nada clara · 5 = totalmente clara." type="list">
+    <dataValidation sqref="G10:G18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no válido" error="Califique con un entero de 1 a 5." promptTitle="Claridad (1-5)" prompt="1 = nada clara · 5 = totalmente clara." type="list">
       <formula1>"1,2,3,4,5"</formula1>
     </dataValidation>
   </dataValidations>

--- a/entregables/gestion-proyectos/Historia_de_usuario_Rehavid_v15.xlsx
+++ b/entregables/gestion-proyectos/Historia_de_usuario_Rehavid_v15.xlsx
@@ -4635,7 +4635,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Abra Mi trabajo con su sesión: la sección «Para resolver como dirección» lista los ajustes de todos los cargos (en la base demostrativa, el Tablero BI de DEM-001). Use «Resolver ajuste» y pruebe las cuatro decisiones.</t>
+          <t>Abra Mi trabajo con su sesión: la sección «Para resolver como dirección» lista los ajustes de todos los cargos (en la demo: el Tablero BI de DEM-001 y la coordinación de DEM-003). Use «Resolver ajuste» y pruebe las cuatro decisiones.</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Su Mi trabajo trae la sección «Para resolver como dirección» con los ajustes de todos los cargos. Resuelva el del Tablero BI demostrativo con contrapropuesta; observe el estado que queda.</t>
+          <t>Su Mi trabajo trae la sección «Para resolver como dirección» con dos casos demo: el Tablero BI de DEM-001 y la coordinación de DEM-003. Resuelva uno con contrapropuesta; observe el estado que queda.</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -5498,17 +5498,17 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Recibir la coordinación Tipo 2 en Mi trabajo</t>
+          <t>Revisar sus coordinaciones Tipo 2 en Mi trabajo</t>
         </is>
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Active un Tipo 2 y abra Mi trabajo.</t>
+          <t>Abra Mi trabajo: la demo trae la coordinación de DEM-001 (aceptada) y la de DEM-003 «En ajuste» con la propuesta que usted mismo hizo por el corrimiento de la parada de mantenimiento.</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
         <is>
-          <t>La coordinación llega como tarjeta independiente con su ciclo propio (validado en la segunda ronda; confirme que sigue igual tras la simplificación).</t>
+          <t>Cada coordinación es una tarjeta independiente con su ciclo y su historial; la que está en ajuste espera la decisión de la dirección.</t>
         </is>
       </c>
       <c r="F11" s="19" t="n"/>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Acepte la asignación de mediciones declarando tiempo y capacidad; en otro producto proponga ajuste.</t>
+          <t>Acepte la «Medición objetiva de carga postural» (DEM-003) que llega pendiente en su bandeja, declarando tiempo y capacidad; en otro producto proponga ajuste.</t>
         </is>
       </c>
       <c r="E12" s="10" t="inlineStr">
@@ -6569,17 +6569,17 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>Revisar la asignación de cápsulas</t>
+          <t>Revisar sus asignaciones de cápsulas</t>
         </is>
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>En Mi trabajo revise su tarjeta de cápsulas.</t>
+          <t>En Mi trabajo revise sus dos tarjetas demo: las cápsulas en curso (DEM-001) y las «Cápsulas de seguridad para líderes de línea» (DEM-002) pendientes, con 120 personas a impactar y su hoja de vida de contenidos definida.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>Muestra horas vendidas y personas a impactar; los botones de aceptar aparecen en la propia tarjeta cuando está pendiente (su N°3: verifique que ahora es visible).</t>
+          <t>Los botones «Aceptar asignación» y «Proponer ajuste» están en la propia tarjeta pendiente (su N°3 de la segunda ronda: verifique que ahora es visible).</t>
         </is>
       </c>
       <c r="F13" s="19" t="n"/>
@@ -6603,7 +6603,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Acepte declarando tiempo y capacidad; en otra asignación proponga ajuste por disponibilidad de producción.</t>
+          <t>Acepte las cápsulas pendientes declarando tiempo y capacidad; luego proponga un ajuste por disponibilidad de producción.</t>
         </is>
       </c>
       <c r="E14" s="10" t="inlineStr">
@@ -7042,7 +7042,7 @@
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>El resumen (Pendientes · En ajuste · Aceptadas · Coordinación) encabeza su bandeja; su producto aparece con las alertas dentro de la tarjeta.</t>
+          <t>Su bandeja demo trae el «Tablero BI de control · fase 2» (DEM-003) pendiente de aceptar y el tablero de DEM-001 en ajuste esperando a la dirección, con las alertas dentro de cada tarjeta.</t>
         </is>
       </c>
       <c r="F12" s="19" t="n"/>
@@ -7066,7 +7066,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Acepte la asignación del tablero; en otra pruebe proponer ajuste y reciba la decisión de la dirección.</t>
+          <t>Acepte la fase 2 declarando tiempo y capacidad; observe en la otra tarjeta la negociación en curso.</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
